--- a/Отчёт по откликам.xlsx
+++ b/Отчёт по откликам.xlsx
@@ -7,7 +7,6 @@
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Лист2_пример заполнения" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -17,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>№</t>
   </si>
@@ -197,41 +196,6 @@
   </si>
   <si>
     <t>https://cloud.mail.ru/public/uVCt/mdgjbadw3</t>
-  </si>
-  <si>
-    <t>Скриншот</t>
-  </si>
-  <si>
-    <t>freelance.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Здравствуйте! Сделаю автоматизацию "без потерь": приём заявки → валидация → запись в базу → журнал событий / уведомление. У меня есть готовое решение — MVP для сбора лидов через Telegram-бота и веб-форму. Всё сохраняется в базу данных, менеджер получает уведомление о каждом лиде. Каналы: Telegram-чат (бот уже работает) + веб-форма. Демо работы системы: https://cloud.mail.ru/public/c3HY/NqqB8HUKJ</t>
-  </si>
-  <si>
-    <t>https://cloud.mail.ru/public/oNch/fAXADcsva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Здравствуйте! У меня есть готовое решение для автоматического сбора лидов — ваш MVP для веб-студии.
-Система принимает заявки через Telegram-бота и веб-форму, сохраняет в базу данных и отправляет уведомление менеджеру. Всё автоматически, ничего не теряется.
-Я могу показать демо работы системы и адаптировать её под ваши задачи.
-Готова обсудить, как это можно использовать для поиска клиентов для студии.
-Демо работы системы: https://cloud.mail.ru/public/c3HY/NqqB8HUKJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Здравствуйте! Вы ищете менеджера по продажам без звонков. Я могу предложить автоматизированное решение, которое заменит часть работы менеджера и будет делать это быстрее и без ошибок.
-Моя система собирает заявки через Telegram-бота, сохраняет их в базу данных и отправляет уведомления менеджеру. Всё автоматически — заявки не теряются, менеджер получает готовые данные для консультации.
-Это MVP, который вы можете внедрить за 1–2 дня.
-Демо работы системы:
-https://cloud.mail.ru/public/c3HY/NqqB8HUKJ</t>
-  </si>
-  <si>
-    <t>https://cloud.mail.ru/public/1Buv/ffDJdZ4wh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Здравствуйте! У меня есть готовое решение для сбора заявок из разных каналов в единую базу данных — ваш MVP для автоматизации. Система принимает сообщения через Telegram-бота и веб-форму, сохраняет их в SQLite и отправляет уведомления о новых обращениях. Всё автоматически, без риска бана, потому что не требует API площадки. Демо работы системы: https://cloud.mail.ru/public/c3HY/NqqB8HUKJ</t>
-  </si>
-  <si>
-    <t>https://cloud.mail.ru/public/ND6Q/9qG66tcvL</t>
   </si>
 </sst>
 </file>
@@ -241,7 +205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -262,12 +226,6 @@
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FF2C3E55"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -290,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -307,15 +265,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -343,20 +292,6 @@
     <tableColumn id="3" name="Дата"/>
     <tableColumn id="4" name="Текст отклика"/>
     <tableColumn id="5" name="Скриншоты"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" displayName="Таблица1" ref="$A:$E">
-  <autoFilter ref="$A:$E"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="№"/>
-    <tableColumn id="2" name="Площадка"/>
-    <tableColumn id="3" name="Дата"/>
-    <tableColumn id="4" name="Текст отклика"/>
-    <tableColumn id="5" name="Скриншот"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1229,250 +1164,4 @@
     <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col bestFit="1" min="1" max="1" width="11.8515625"/>
-    <col customWidth="1" min="2" max="2" width="35.421875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="13.8515625"/>
-    <col customWidth="1" min="4" max="4" style="2" width="53.140625"/>
-    <col customWidth="1" min="5" max="5" width="85.140625"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" ht="128.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46210</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" ht="228">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="1">
-        <v>46210</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" ht="213.75">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46210</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" ht="178.5" customHeight="1">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46210</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" ht="15">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" ht="15">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="E2"/>
-    <hyperlink r:id="rId1" ref="E3"/>
-    <hyperlink r:id="rId2" ref="E4"/>
-    <hyperlink r:id="rId3" ref="E5"/>
-  </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <tableParts count="1">
-    <tablePart r:id="rId4"/>
-  </tableParts>
-</worksheet>
 </file>